--- a/02_DIA_inicio_2026_analisis_assets/rbd_9695_liceo-polivalente-eugenio-pereira-salas_nt2_rubricas.xlsx
+++ b/02_DIA_inicio_2026_analisis_assets/rbd_9695_liceo-polivalente-eugenio-pereira-salas_nt2_rubricas.xlsx
@@ -1992,13 +1992,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2D34FFF5-AD4A-47F1-8DED-CF32CA0B4312}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A4D916B2-8AAB-43EA-A0D4-F62FF8679AB6}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FDA29027-EA16-412C-9641-D99FCD9360F1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FF329800-92AD-4071-9308-4742219861B4}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{55823F11-52B3-4A02-BC09-A2376B062E98}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F0DAF2D8-A313-46A2-AA2C-3646AB2FB311}"/>
 </file>